--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 02/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
@@ -434,17 +434,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -456,23 +451,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.00872</v>
+        <v>17.04266</v>
       </c>
       <c r="D2" t="n">
-        <v>17.2572</v>
+        <v>16.24589</v>
       </c>
       <c r="E2" t="n">
-        <v>16.94081</v>
+        <v>16.62877</v>
+      </c>
+      <c r="F2" t="n">
+        <v>22.07338</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05146</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.85422</v>
+        <v>34.61197</v>
       </c>
     </row>
     <row r="3">
@@ -482,22 +477,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.01216</v>
+        <v>16.77369</v>
       </c>
       <c r="D3" t="n">
-        <v>16.67429</v>
+        <v>16.28293</v>
       </c>
       <c r="E3" t="n">
-        <v>16.68961</v>
+        <v>16.628</v>
       </c>
       <c r="F3" t="n">
-        <v>42.71607</v>
+        <v>21.91074</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.87624</v>
+        <v>34.55894</v>
       </c>
     </row>
     <row r="4">
@@ -506,25 +498,20 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="C4" t="n">
+        <v>16.85152</v>
       </c>
       <c r="D4" t="n">
-        <v>16.80939</v>
+        <v>15.75856</v>
       </c>
       <c r="E4" t="n">
-        <v>17.05923</v>
+        <v>16.63107</v>
       </c>
       <c r="F4" t="n">
-        <v>43.47739</v>
+        <v>22.21256</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05056</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.86905</v>
+        <v>34.59639</v>
       </c>
     </row>
     <row r="5">
@@ -533,25 +520,20 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
+      <c r="C5" t="n">
+        <v>16.64155</v>
       </c>
       <c r="D5" t="n">
-        <v>16.55719</v>
+        <v>15.96116</v>
       </c>
       <c r="E5" t="n">
-        <v>16.74461</v>
+        <v>16.62067</v>
       </c>
       <c r="F5" t="n">
-        <v>42.5912</v>
+        <v>21.81466</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05153</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.84728</v>
+        <v>34.37177</v>
       </c>
     </row>
     <row r="6">
@@ -561,22 +543,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.98061</v>
+        <v>16.88321</v>
       </c>
       <c r="D6" t="n">
-        <v>16.79817</v>
+        <v>16.12544</v>
       </c>
       <c r="E6" t="n">
-        <v>16.72935</v>
+        <v>16.68258</v>
       </c>
       <c r="F6" t="n">
-        <v>42.27256</v>
+        <v>22.00355</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0503</v>
-      </c>
-      <c r="H6" t="e">
-        <v>#DIV/0!</v>
+        <v>34.91057</v>
       </c>
     </row>
     <row r="7">
@@ -586,24 +565,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.05141</v>
+        <v>16.90649</v>
       </c>
       <c r="D7" t="n">
-        <v>16.74289</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 16.48 </t>
-        </is>
+        <v>16.43679</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.66665</v>
       </c>
       <c r="F7" t="n">
-        <v>42.68469</v>
+        <v>22.10963</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05103</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.82074</v>
+        <v>33.96711</v>
       </c>
     </row>
     <row r="8">
@@ -613,22 +587,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.20222</v>
+        <v>17.07107</v>
       </c>
       <c r="D8" t="n">
-        <v>16.96244</v>
+        <v>16.19984</v>
       </c>
       <c r="E8" t="n">
-        <v>17.33626</v>
+        <v>16.5169</v>
       </c>
       <c r="F8" t="n">
-        <v>43.03199</v>
+        <v>22.36665</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0514</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.8626</v>
+        <v>35.10658</v>
       </c>
     </row>
     <row r="9">
@@ -638,22 +609,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.34257</v>
+        <v>16.9717</v>
       </c>
       <c r="D9" t="n">
-        <v>16.94327</v>
+        <v>16.40415</v>
       </c>
       <c r="E9" t="n">
-        <v>16.59486</v>
+        <v>16.43452</v>
       </c>
       <c r="F9" t="n">
-        <v>42.35536</v>
+        <v>22.11573</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05194</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.86935</v>
+        <v>34.59377</v>
       </c>
     </row>
     <row r="10">
@@ -663,31 +631,48 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.88291</v>
+        <v>16.85638</v>
       </c>
       <c r="D10" t="n">
-        <v>16.73797</v>
+        <v>16.03933</v>
       </c>
       <c r="E10" t="n">
-        <v>16.72438</v>
+        <v>16.73486</v>
       </c>
       <c r="F10" t="n">
-        <v>42.98479</v>
+        <v>21.91259</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05108</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.85123</v>
+        <v>34.63206</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -701,14 +686,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>17.10763</v>
       </c>
       <c r="D12" t="n">
-        <v>1.09552</v>
+        <v>16.51965</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.8371</v>
+      </c>
+      <c r="F12" t="n">
+        <v>43.16442</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05042</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.83513</v>
       </c>
     </row>
     <row r="13">
@@ -718,10 +715,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>17.38794</v>
       </c>
       <c r="D13" t="n">
-        <v>1.10902</v>
+        <v>16.8149</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.31053</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43.63544</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05253</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.84372</v>
       </c>
     </row>
     <row r="14">
@@ -731,10 +740,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>16.96488</v>
       </c>
       <c r="D14" t="n">
-        <v>1.14399</v>
+        <v>16.75492</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.92424</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.74019</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05152</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.81742</v>
       </c>
     </row>
     <row r="15">
@@ -744,10 +765,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>17.2572</v>
       </c>
       <c r="D15" t="n">
-        <v>1.13238</v>
+        <v>16.94081</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.00872</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.60954</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05146</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.85422</v>
       </c>
     </row>
     <row r="16">
@@ -757,10 +790,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>17.01216</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1143</v>
+        <v>16.67429</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.68961</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42.71607</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05124</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.87624</v>
       </c>
     </row>
     <row r="17">
@@ -770,10 +815,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>17.05923</v>
       </c>
       <c r="D17" t="n">
-        <v>1.13363</v>
+        <v>16.80939</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.8982</v>
+      </c>
+      <c r="F17" t="n">
+        <v>43.47739</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.86905</v>
       </c>
     </row>
     <row r="18">
@@ -783,10 +840,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>16.74461</v>
       </c>
       <c r="D18" t="n">
-        <v>1.13638</v>
+        <v>16.5373</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.55719</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.5912</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05153</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.84728</v>
       </c>
     </row>
     <row r="19">
@@ -796,10 +865,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>16.98061</v>
       </c>
       <c r="D19" t="n">
-        <v>1.13164</v>
+        <v>16.72935</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.79817</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.27256</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.80551</v>
       </c>
     </row>
     <row r="20">
@@ -809,10 +890,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>17.16456</v>
       </c>
       <c r="D20" t="n">
-        <v>1.13734</v>
+        <v>16.74289</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17.05141</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.68469</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05103</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.82074</v>
       </c>
     </row>
   </sheetData>
